--- a/import-files/App Lower Rankings.xlsx
+++ b/import-files/App Lower Rankings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF19F4C9-ECE9-462B-8B89-60F14067D835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10745110-F8F7-408D-B657-E15C0D5DE74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="177">
   <si>
     <t>Age Group</t>
   </si>
@@ -564,6 +564,9 @@
   </si>
   <si>
     <t>DSA-100001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -   </t>
   </si>
 </sst>
 </file>
@@ -576,7 +579,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,6 +600,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -612,7 +628,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -629,6 +645,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF95B3D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -636,7 +661,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -672,6 +697,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -971,7 +1008,7 @@
     <col min="9" max="11" width="3.75" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="6.25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.25" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="6.25" bestFit="1" customWidth="1"/>
   </cols>
@@ -1031,25 +1068,25 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="9">
-        <v>11896</v>
+        <v>11825</v>
       </c>
       <c r="F2" s="9">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="G2" s="10">
-        <v>52.405286343612332</v>
+        <v>52.63</v>
       </c>
       <c r="H2" s="11">
         <v>1</v>
@@ -1057,12 +1094,10 @@
       <c r="I2" s="9">
         <v>24</v>
       </c>
-      <c r="J2" s="9">
-        <v>1</v>
-      </c>
+      <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="M2" s="9">
         <v>24</v>
@@ -1071,61 +1106,61 @@
         <v>19</v>
       </c>
       <c r="O2" s="12">
-        <v>0.79166666666666663</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="P2" s="11">
-        <v>61.923230118732874</v>
+        <v>62.2</v>
       </c>
       <c r="Q2" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="9">
-        <v>11469</v>
+        <v>13892</v>
       </c>
       <c r="F3" s="9">
-        <v>699</v>
+        <v>788</v>
       </c>
       <c r="G3" s="10">
-        <v>49.223175965665234</v>
+        <v>52.89</v>
       </c>
       <c r="H3" s="11">
-        <v>0.78260869565217395</v>
+        <v>1</v>
       </c>
       <c r="I3" s="9">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J3" s="9">
         <v>1</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="M3" s="9">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="N3" s="9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O3" s="12">
-        <v>0.86956521739130432</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="P3" s="11">
-        <v>61.688560832351058</v>
+        <v>62</v>
       </c>
       <c r="Q3" s="9">
         <v>2</v>
@@ -1133,102 +1168,102 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="9">
-        <v>9821</v>
+        <v>9807</v>
       </c>
       <c r="F4" s="9">
-        <v>579</v>
+        <v>539</v>
       </c>
       <c r="G4" s="10">
-        <v>50.886010362694293</v>
+        <v>54.58</v>
       </c>
       <c r="H4" s="11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I4" s="9">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="9">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M4" s="9">
         <v>20</v>
       </c>
       <c r="N4" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O4" s="12">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="P4" s="11">
-        <v>59.688873569274939</v>
+        <v>60</v>
       </c>
       <c r="Q4" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="9">
-        <v>11584</v>
+        <v>13401</v>
       </c>
       <c r="F5" s="9">
-        <v>738</v>
+        <v>820</v>
       </c>
       <c r="G5" s="10">
-        <v>47.089430894308947</v>
+        <v>49.03</v>
       </c>
       <c r="H5" s="11">
-        <v>0.54166666666666663</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="9">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J5" s="9">
         <v>2</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M5" s="9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N5" s="9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O5" s="12">
-        <v>0.83333333333333337</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="P5" s="11">
-        <v>59.582230965582745</v>
+        <v>59.8</v>
       </c>
       <c r="Q5" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -1245,19 +1280,19 @@
         <v>15</v>
       </c>
       <c r="E6" s="9">
-        <v>11820</v>
+        <v>12321</v>
       </c>
       <c r="F6" s="9">
-        <v>734</v>
+        <v>766</v>
       </c>
       <c r="G6" s="10">
-        <v>48.310626702997283</v>
+        <v>48.25</v>
       </c>
       <c r="H6" s="11">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I6" s="9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
@@ -1265,16 +1300,16 @@
         <v>69</v>
       </c>
       <c r="M6" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N6" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O6" s="12">
-        <v>0.79166666666666663</v>
+        <v>0.8</v>
       </c>
       <c r="P6" s="11">
-        <v>58.542299188597418</v>
+        <v>58.7</v>
       </c>
       <c r="Q6" s="9">
         <v>3</v>
@@ -1282,53 +1317,53 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="9">
+        <v>13470</v>
+      </c>
+      <c r="F7" s="9">
+        <v>857</v>
+      </c>
+      <c r="G7" s="10">
+        <v>47.15</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="9">
         <v>14</v>
-      </c>
-      <c r="E7" s="9">
-        <v>12557</v>
-      </c>
-      <c r="F7" s="9">
-        <v>727</v>
-      </c>
-      <c r="G7" s="10">
-        <v>51.817056396148558</v>
-      </c>
-      <c r="H7" s="11">
-        <v>0.76923076923076927</v>
-      </c>
-      <c r="I7" s="9">
-        <v>20</v>
       </c>
       <c r="J7" s="9">
         <v>2</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M7" s="9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O7" s="12">
-        <v>0.65384615384615385</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="P7" s="11">
-        <v>57.543125878721298</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1351,7 +1386,7 @@
         <v>576</v>
       </c>
       <c r="G8" s="10">
-        <v>50.166666666666664</v>
+        <v>50.17</v>
       </c>
       <c r="H8" s="11">
         <v>0.9</v>
@@ -1376,7 +1411,7 @@
         <v>0.7</v>
       </c>
       <c r="P8" s="11">
-        <v>56.920072184879281</v>
+        <v>56.9</v>
       </c>
       <c r="Q8" s="9">
         <v>3</v>
@@ -1384,50 +1419,54 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="9">
-        <v>7803</v>
+        <v>13853</v>
       </c>
       <c r="F9" s="9">
-        <v>438</v>
+        <v>848</v>
       </c>
       <c r="G9" s="10">
-        <v>53.445205479452056</v>
+        <v>49.01</v>
       </c>
       <c r="H9" s="11">
-        <v>0.6875</v>
+        <v>0.8</v>
       </c>
       <c r="I9" s="9">
-        <v>11</v>
-      </c>
-      <c r="J9" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="J9" s="9">
+        <v>1</v>
+      </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="M9" s="9">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O9" s="12">
-        <v>0.625</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="P9" s="11">
-        <v>56.901563554160425</v>
-      </c>
-      <c r="Q9" s="9"/>
+        <v>56.9</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -1443,47 +1482,49 @@
         <v>15</v>
       </c>
       <c r="E10" s="9">
-        <v>13808</v>
+        <v>15812</v>
       </c>
       <c r="F10" s="9">
-        <v>882</v>
+        <v>999</v>
       </c>
       <c r="G10" s="10">
-        <v>46.965986394557824</v>
+        <v>47.48</v>
       </c>
       <c r="H10" s="11">
-        <v>0.5714285714285714</v>
+        <v>0.6</v>
       </c>
       <c r="I10" s="9">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="J10" s="9">
+        <v>1</v>
+      </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9">
         <v>84</v>
       </c>
       <c r="M10" s="9">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N10" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O10" s="12">
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="P10" s="11">
-        <v>55.432512732804604</v>
+        <v>56.9</v>
       </c>
       <c r="Q10" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>24</v>
@@ -1492,16 +1533,16 @@
         <v>14</v>
       </c>
       <c r="E11" s="9">
-        <v>11248</v>
+        <v>13503</v>
       </c>
       <c r="F11" s="9">
-        <v>700</v>
+        <v>844</v>
       </c>
       <c r="G11" s="10">
-        <v>48.205714285714279</v>
+        <v>48</v>
       </c>
       <c r="H11" s="11">
-        <v>0.875</v>
+        <v>0.8</v>
       </c>
       <c r="I11" s="9">
         <v>21</v>
@@ -1509,79 +1550,81 @@
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="M11" s="9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O11" s="12">
-        <v>0.70833333333333337</v>
+        <v>0.67900000000000005</v>
       </c>
       <c r="P11" s="11">
-        <v>55.405503118063052</v>
+        <v>55.5</v>
       </c>
       <c r="Q11" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="9">
-        <v>9848</v>
+        <v>14266</v>
       </c>
       <c r="F12" s="9">
-        <v>596</v>
+        <v>831</v>
       </c>
       <c r="G12" s="10">
-        <v>49.570469798657712</v>
+        <v>51.5</v>
       </c>
       <c r="H12" s="11">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="I12" s="9">
-        <v>5</v>
-      </c>
-      <c r="J12" s="9"/>
+        <v>24</v>
+      </c>
+      <c r="J12" s="9">
+        <v>2</v>
+      </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N12" s="9">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O12" s="12">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="P12" s="11">
-        <v>55.261046547067011</v>
+        <v>55.5</v>
       </c>
       <c r="Q12" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>35</v>
@@ -1590,26 +1633,24 @@
         <v>14</v>
       </c>
       <c r="E13" s="9">
-        <v>11849</v>
+        <v>11798</v>
       </c>
       <c r="F13" s="9">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="G13" s="10">
-        <v>48.036486486486488</v>
+        <v>49.02</v>
       </c>
       <c r="H13" s="11">
-        <v>0.70833333333333337</v>
+        <v>0.3</v>
       </c>
       <c r="I13" s="9">
-        <v>17</v>
-      </c>
-      <c r="J13" s="9">
-        <v>1</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="M13" s="9">
         <v>24</v>
@@ -1618,12 +1659,14 @@
         <v>16</v>
       </c>
       <c r="O13" s="12">
-        <v>0.66666666666666663</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="P13" s="11">
-        <v>54.833450965898841</v>
-      </c>
-      <c r="Q13" s="9"/>
+        <v>55.4</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
@@ -1645,10 +1688,10 @@
         <v>488</v>
       </c>
       <c r="G14" s="10">
-        <v>46.672131147540981</v>
+        <v>46.67</v>
       </c>
       <c r="H14" s="11">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="I14" s="9">
         <v>10</v>
@@ -1665,10 +1708,10 @@
         <v>11</v>
       </c>
       <c r="O14" s="12">
-        <v>0.6875</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="P14" s="11">
-        <v>54.429811111780936</v>
+        <v>54.4</v>
       </c>
       <c r="Q14" s="9">
         <v>1</v>
@@ -1694,10 +1737,10 @@
         <v>818</v>
       </c>
       <c r="G15" s="10">
-        <v>49.485330073349637</v>
+        <v>49.49</v>
       </c>
       <c r="H15" s="11">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="I15" s="9">
         <v>35</v>
@@ -1714,10 +1757,10 @@
         <v>17</v>
       </c>
       <c r="O15" s="12">
-        <v>0.6071428571428571</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="P15" s="11">
-        <v>54.279422113212867</v>
+        <v>54.3</v>
       </c>
       <c r="Q15" s="9">
         <v>4</v>
@@ -1737,19 +1780,19 @@
         <v>14</v>
       </c>
       <c r="E16" s="9">
-        <v>11680</v>
+        <v>13622</v>
       </c>
       <c r="F16" s="9">
-        <v>732</v>
+        <v>842</v>
       </c>
       <c r="G16" s="10">
-        <v>47.868852459016395</v>
+        <v>48.53</v>
       </c>
       <c r="H16" s="11">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I16" s="9">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -1759,16 +1802,16 @@
         <v>74</v>
       </c>
       <c r="M16" s="9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O16" s="12">
-        <v>0.66666666666666663</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="P16" s="11">
-        <v>54.170149356319797</v>
+        <v>54</v>
       </c>
       <c r="Q16" s="9">
         <v>2</v>
@@ -1776,48 +1819,48 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="9">
-        <v>11499</v>
+        <v>12819</v>
       </c>
       <c r="F17" s="9">
-        <v>734</v>
+        <v>840</v>
       </c>
       <c r="G17" s="10">
-        <v>46.998637602179841</v>
+        <v>45.78</v>
       </c>
       <c r="H17" s="11">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="I17" s="9">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="M17" s="9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N17" s="9">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O17" s="12">
-        <v>0.625</v>
+        <v>0.69199999999999995</v>
       </c>
       <c r="P17" s="11">
-        <v>53.320331772244337</v>
+        <v>53.8</v>
       </c>
       <c r="Q17" s="9">
         <v>2</v>
@@ -1825,100 +1868,100 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="9">
-        <v>10815</v>
+        <v>12199</v>
       </c>
       <c r="F18" s="9">
-        <v>694</v>
+        <v>738</v>
       </c>
       <c r="G18" s="10">
-        <v>46.750720461095099</v>
+        <v>49.59</v>
       </c>
       <c r="H18" s="11">
-        <v>0.86363636363636365</v>
+        <v>0.3</v>
       </c>
       <c r="I18" s="9">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="M18" s="9">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="N18" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O18" s="12">
-        <v>0.63636363636363635</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="P18" s="11">
-        <v>52.750181417095135</v>
+        <v>53.3</v>
       </c>
       <c r="Q18" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="9">
-        <v>10379</v>
+        <v>13054</v>
       </c>
       <c r="F19" s="9">
-        <v>629</v>
+        <v>817</v>
       </c>
       <c r="G19" s="10">
-        <v>49.502384737678859</v>
+        <v>47.93</v>
       </c>
       <c r="H19" s="11">
-        <v>0.36363636363636365</v>
+        <v>0.8</v>
       </c>
       <c r="I19" s="9">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="M19" s="9">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O19" s="12">
-        <v>0.54545454545454541</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="P19" s="11">
-        <v>52.430167383230668</v>
+        <v>52.3</v>
       </c>
       <c r="Q19" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1941,10 +1984,10 @@
         <v>476</v>
       </c>
       <c r="G20" s="10">
-        <v>47.256302521008408</v>
+        <v>47.26</v>
       </c>
       <c r="H20" s="11">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="I20" s="9">
         <v>6</v>
@@ -1964,7 +2007,7 @@
         <v>0.625</v>
       </c>
       <c r="P20" s="11">
-        <v>52.121671085439935</v>
+        <v>52.1</v>
       </c>
       <c r="Q20" s="9">
         <v>2</v>
@@ -1972,106 +2015,110 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" s="9">
-        <v>12629</v>
+        <v>7377</v>
       </c>
       <c r="F21" s="9">
-        <v>843</v>
+        <v>408</v>
       </c>
       <c r="G21" s="10">
-        <v>44.943060498220639</v>
+        <v>54.24</v>
       </c>
       <c r="H21" s="11">
-        <v>0.65384615384615385</v>
+        <v>0.9</v>
       </c>
       <c r="I21" s="9">
-        <v>17</v>
-      </c>
-      <c r="J21" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="J21" s="9">
+        <v>1</v>
+      </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="M21" s="9">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N21" s="9">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O21" s="12">
-        <v>0.61538461538461542</v>
+        <v>0.438</v>
       </c>
       <c r="P21" s="11">
-        <v>50.95307574620395</v>
+        <v>51.9</v>
       </c>
       <c r="Q21" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22" s="9">
-        <v>7860</v>
+        <v>13613</v>
       </c>
       <c r="F22" s="9">
-        <v>534</v>
+        <v>902</v>
       </c>
       <c r="G22" s="10">
-        <v>44.157303370786515</v>
+        <v>45.28</v>
       </c>
       <c r="H22" s="11">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="I22" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="M22" s="9">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O22" s="12">
-        <v>0.625</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="P22" s="11">
-        <v>50.83053409623912</v>
-      </c>
-      <c r="Q22" s="9"/>
+        <v>50.9</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>60</v>
@@ -2080,40 +2127,38 @@
         <v>14</v>
       </c>
       <c r="E23" s="9">
-        <v>11576</v>
+        <v>9723</v>
       </c>
       <c r="F23" s="9">
-        <v>746</v>
+        <v>657</v>
       </c>
       <c r="G23" s="10">
-        <v>46.552278820375335</v>
+        <v>44.4</v>
       </c>
       <c r="H23" s="11">
-        <v>8.3333333333333329E-2</v>
+        <v>0.7</v>
       </c>
       <c r="I23" s="9">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="M23" s="9">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N23" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O23" s="12">
-        <v>0.54166666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="P23" s="11">
-        <v>49.54581048817753</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>2</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q23" s="9"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -2135,10 +2180,10 @@
         <v>607</v>
       </c>
       <c r="G24" s="10">
-        <v>45.95387149917628</v>
+        <v>45.95</v>
       </c>
       <c r="H24" s="11">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="I24" s="9">
         <v>7</v>
@@ -2158,7 +2203,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="P24" s="11">
-        <v>49.468874191157603</v>
+        <v>49.5</v>
       </c>
       <c r="Q24" s="9">
         <v>1</v>
@@ -2166,10 +2211,10 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>60</v>
@@ -2178,39 +2223,41 @@
         <v>15</v>
       </c>
       <c r="E25" s="9">
-        <v>8616</v>
+        <v>13244</v>
       </c>
       <c r="F25" s="9">
-        <v>573</v>
+        <v>916</v>
       </c>
       <c r="G25" s="10">
-        <v>45.109947643979055</v>
+        <v>43.38</v>
       </c>
       <c r="H25" s="11">
         <v>0.5</v>
       </c>
       <c r="I25" s="9">
-        <v>9</v>
-      </c>
-      <c r="J25" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="J25" s="9">
+        <v>1</v>
+      </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="M25" s="9">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O25" s="12">
-        <v>0.55555555555555558</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="P25" s="11">
-        <v>49.202909574767823</v>
+        <v>49.2</v>
       </c>
       <c r="Q25" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -2233,10 +2280,10 @@
         <v>875</v>
       </c>
       <c r="G26" s="10">
-        <v>45.668571428571425</v>
+        <v>45.67</v>
       </c>
       <c r="H26" s="11">
-        <v>0.4642857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="I26" s="9">
         <v>13</v>
@@ -2253,10 +2300,10 @@
         <v>15</v>
       </c>
       <c r="O26" s="12">
-        <v>0.5357142857142857</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="P26" s="11">
-        <v>49.126608057497243</v>
+        <v>49.1</v>
       </c>
       <c r="Q26" s="9">
         <v>2</v>
@@ -2264,48 +2311,48 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="9">
-        <v>9411</v>
+        <v>13470</v>
       </c>
       <c r="F27" s="9">
-        <v>617</v>
+        <v>877</v>
       </c>
       <c r="G27" s="10">
-        <v>45.758508914100489</v>
+        <v>46.08</v>
       </c>
       <c r="H27" s="11">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I27" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="M27" s="9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O27" s="12">
-        <v>0.55000000000000004</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="P27" s="11">
-        <v>48.974248346523552</v>
+        <v>49.1</v>
       </c>
       <c r="Q27" s="9">
         <v>2</v>
@@ -2313,110 +2360,108 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E28" s="9">
-        <v>11458</v>
+        <v>9411</v>
       </c>
       <c r="F28" s="9">
-        <v>760</v>
+        <v>617</v>
       </c>
       <c r="G28" s="10">
-        <v>45.228947368421053</v>
+        <v>45.76</v>
       </c>
       <c r="H28" s="11">
-        <v>0.16666666666666666</v>
+        <v>0.3</v>
       </c>
       <c r="I28" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M28" s="9">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N28" s="9">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O28" s="12">
-        <v>0.54166666666666663</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="P28" s="11">
-        <v>48.649349931609386</v>
+        <v>49</v>
       </c>
       <c r="Q28" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E29" s="9">
-        <v>11260</v>
+        <v>13213</v>
       </c>
       <c r="F29" s="9">
-        <v>780</v>
+        <v>868</v>
       </c>
       <c r="G29" s="10">
-        <v>43.307692307692307</v>
+        <v>45.67</v>
       </c>
       <c r="H29" s="11">
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="I29" s="9">
-        <v>8</v>
-      </c>
-      <c r="J29" s="9">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="9">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="M29" s="9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O29" s="12">
-        <v>0.58333333333333337</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="P29" s="11">
-        <v>48.45510031868789</v>
+        <v>48.7</v>
       </c>
       <c r="Q29" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>60</v>
@@ -2425,16 +2470,16 @@
         <v>14</v>
       </c>
       <c r="E30" s="9">
-        <v>11410</v>
+        <v>7631</v>
       </c>
       <c r="F30" s="9">
-        <v>806</v>
+        <v>528</v>
       </c>
       <c r="G30" s="10">
-        <v>42.468982630272954</v>
+        <v>43.36</v>
       </c>
       <c r="H30" s="11">
-        <v>0.375</v>
+        <v>0.6</v>
       </c>
       <c r="I30" s="9">
         <v>9</v>
@@ -2442,22 +2487,22 @@
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="M30" s="9">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N30" s="9">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O30" s="12">
-        <v>0.58333333333333337</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="P30" s="11">
-        <v>47.913027244730479</v>
+        <v>47.8</v>
       </c>
       <c r="Q30" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -2480,10 +2525,10 @@
         <v>862</v>
       </c>
       <c r="G31" s="10">
-        <v>46.545243619489561</v>
+        <v>46.55</v>
       </c>
       <c r="H31" s="11">
-        <v>0.8928571428571429</v>
+        <v>0.9</v>
       </c>
       <c r="I31" s="9">
         <v>25</v>
@@ -2502,10 +2547,10 @@
         <v>13</v>
       </c>
       <c r="O31" s="12">
-        <v>0.4642857142857143</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="P31" s="11">
-        <v>47.540289670761396</v>
+        <v>47.5</v>
       </c>
       <c r="Q31" s="9">
         <v>1</v>
@@ -2513,99 +2558,99 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="9">
-        <v>9709</v>
+        <v>8928</v>
       </c>
       <c r="F32" s="9">
-        <v>678</v>
+        <v>619</v>
       </c>
       <c r="G32" s="10">
-        <v>42.960176991150441</v>
+        <v>43.27</v>
       </c>
       <c r="H32" s="11">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I32" s="9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
       <c r="L32" s="9">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M32" s="9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N32" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O32" s="12">
-        <v>0.55000000000000004</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="P32" s="11">
-        <v>47.095130875285108</v>
-      </c>
-      <c r="Q32" s="9">
-        <v>1</v>
-      </c>
+        <v>46.8</v>
+      </c>
+      <c r="Q32" s="9"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="9">
-        <v>8928</v>
+        <v>10289</v>
       </c>
       <c r="F33" s="9">
-        <v>619</v>
+        <v>697</v>
       </c>
       <c r="G33" s="10">
-        <v>43.269789983844909</v>
+        <v>44.29</v>
       </c>
       <c r="H33" s="11">
-        <v>0.26315789473684209</v>
+        <v>0.5</v>
       </c>
       <c r="I33" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="9">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M33" s="9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N33" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O33" s="12">
-        <v>0.52631578947368418</v>
+        <v>0.5</v>
       </c>
       <c r="P33" s="11">
-        <v>46.84091368563525</v>
-      </c>
-      <c r="Q33" s="9"/>
+        <v>46.8</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>2</v>
+      </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
@@ -2627,10 +2672,10 @@
         <v>484</v>
       </c>
       <c r="G34" s="10">
-        <v>46.196280991735541</v>
+        <v>46.2</v>
       </c>
       <c r="H34" s="11">
-        <v>0.4375</v>
+        <v>0.4</v>
       </c>
       <c r="I34" s="9">
         <v>7</v>
@@ -2647,10 +2692,10 @@
         <v>7</v>
       </c>
       <c r="O34" s="12">
-        <v>0.4375</v>
+        <v>0.438</v>
       </c>
       <c r="P34" s="11">
-        <v>46.159036608037688</v>
+        <v>46.2</v>
       </c>
       <c r="Q34" s="9">
         <v>2</v>
@@ -2658,155 +2703,159 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="9">
-        <v>10381</v>
+        <v>11154</v>
       </c>
       <c r="F35" s="9">
-        <v>700</v>
+        <v>749</v>
       </c>
       <c r="G35" s="10">
-        <v>44.49</v>
+        <v>44.68</v>
       </c>
       <c r="H35" s="11">
-        <v>0.54545454545454541</v>
+        <v>0.4</v>
       </c>
       <c r="I35" s="9">
-        <v>12</v>
-      </c>
-      <c r="J35" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="J35" s="9">
+        <v>1</v>
+      </c>
       <c r="K35" s="9"/>
       <c r="L35" s="9">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="M35" s="9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N35" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O35" s="12">
-        <v>0.45454545454545453</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="P35" s="11">
-        <v>45.674434257166943</v>
-      </c>
-      <c r="Q35" s="9"/>
+        <v>46.1</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="9">
-        <v>9096</v>
+        <v>10381</v>
       </c>
       <c r="F36" s="9">
-        <v>625</v>
+        <v>700</v>
       </c>
       <c r="G36" s="10">
-        <v>43.660799999999995</v>
+        <v>44.49</v>
       </c>
       <c r="H36" s="11">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="I36" s="9">
-        <v>9</v>
-      </c>
-      <c r="J36" s="9">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="J36" s="9"/>
       <c r="K36" s="9"/>
       <c r="L36" s="9">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M36" s="9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N36" s="9">
         <v>10</v>
       </c>
       <c r="O36" s="12">
-        <v>0.5</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="P36" s="11">
-        <v>44.762184231552339</v>
+        <v>45.7</v>
       </c>
       <c r="Q36" s="9"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E37" s="9">
-        <v>11127</v>
+        <v>11085</v>
       </c>
       <c r="F37" s="9">
-        <v>779</v>
+        <v>744</v>
       </c>
       <c r="G37" s="10">
-        <v>42.851091142490375</v>
+        <v>44.7</v>
       </c>
       <c r="H37" s="11">
         <v>0.5</v>
       </c>
       <c r="I37" s="9">
-        <v>12</v>
-      </c>
-      <c r="J37" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="J37" s="9">
+        <v>1</v>
+      </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M37" s="9">
         <v>24</v>
       </c>
       <c r="N37" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O37" s="12">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="P37" s="11">
-        <v>44.544170401866943</v>
+        <v>45.7</v>
       </c>
       <c r="Q37" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>60</v>
@@ -2815,159 +2864,161 @@
         <v>14</v>
       </c>
       <c r="E38" s="9">
-        <v>8318</v>
+        <v>13046</v>
       </c>
       <c r="F38" s="9">
-        <v>577</v>
+        <v>923</v>
       </c>
       <c r="G38" s="10">
-        <v>43.247833622183705</v>
+        <v>42.4</v>
       </c>
       <c r="H38" s="11">
-        <v>0.27777777777777779</v>
+        <v>0.4</v>
       </c>
       <c r="I38" s="9">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
       <c r="L38" s="9">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="M38" s="9">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O38" s="12">
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="P38" s="11">
-        <v>44.469642945480274</v>
-      </c>
-      <c r="Q38" s="9"/>
+        <v>45.4</v>
+      </c>
+      <c r="Q38" s="9">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" s="9">
-        <v>9300</v>
+        <v>10335</v>
       </c>
       <c r="F39" s="9">
-        <v>624</v>
+        <v>738</v>
       </c>
       <c r="G39" s="10">
-        <v>44.71153846153846</v>
+        <v>42.01</v>
       </c>
       <c r="H39" s="11">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
       <c r="I39" s="9">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
       <c r="L39" s="9">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="M39" s="9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N39" s="9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O39" s="12">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="P39" s="11">
-        <v>43.021712310737676</v>
-      </c>
-      <c r="Q39" s="9"/>
+        <v>44.8</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E40" s="9">
-        <v>10059</v>
+        <v>11278</v>
       </c>
       <c r="F40" s="9">
-        <v>677</v>
+        <v>736</v>
       </c>
       <c r="G40" s="10">
-        <v>44.574593796159533</v>
+        <v>45.97</v>
       </c>
       <c r="H40" s="11">
-        <v>0.31818181818181818</v>
+        <v>0.7</v>
       </c>
       <c r="I40" s="9">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
       <c r="L40" s="9">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M40" s="9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N40" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O40" s="12">
-        <v>0.36363636363636365</v>
+        <v>0.375</v>
       </c>
       <c r="P40" s="11">
-        <v>42.872913623067355</v>
-      </c>
-      <c r="Q40" s="9">
-        <v>1</v>
-      </c>
+        <v>44.5</v>
+      </c>
+      <c r="Q40" s="9"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E41" s="9">
-        <v>11475</v>
+        <v>12862</v>
       </c>
       <c r="F41" s="9">
-        <v>768</v>
+        <v>908</v>
       </c>
       <c r="G41" s="10">
-        <v>44.82421875</v>
+        <v>42.5</v>
       </c>
       <c r="H41" s="11">
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="I41" s="9">
         <v>14</v>
@@ -2975,43 +3026,45 @@
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
       <c r="L41" s="9">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="M41" s="9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O41" s="12">
-        <v>0.33333333333333331</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="P41" s="11">
-        <v>42.615990835074882</v>
-      </c>
-      <c r="Q41" s="9"/>
+        <v>43.3</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>2</v>
+      </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E42" s="9">
-        <v>9150</v>
+        <v>9323</v>
       </c>
       <c r="F42" s="9">
-        <v>628</v>
+        <v>678</v>
       </c>
       <c r="G42" s="10">
-        <v>43.710191082802545</v>
+        <v>41.25</v>
       </c>
       <c r="H42" s="11">
         <v>0.4</v>
@@ -3019,24 +3072,22 @@
       <c r="I42" s="9">
         <v>8</v>
       </c>
-      <c r="J42" s="9">
-        <v>1</v>
-      </c>
+      <c r="J42" s="9"/>
       <c r="K42" s="9"/>
       <c r="L42" s="9">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M42" s="9">
         <v>20</v>
       </c>
       <c r="N42" s="9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O42" s="12">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="P42" s="11">
-        <v>42.148758882030698</v>
+        <v>42.9</v>
       </c>
       <c r="Q42" s="9">
         <v>1</v>
@@ -3044,78 +3095,80 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E43" s="9">
-        <v>10398</v>
+        <v>11035</v>
       </c>
       <c r="F43" s="9">
-        <v>768</v>
+        <v>737</v>
       </c>
       <c r="G43" s="10">
-        <v>40.6171875</v>
+        <v>44.92</v>
       </c>
       <c r="H43" s="11">
-        <v>0.31818181818181818</v>
+        <v>0.3</v>
       </c>
       <c r="I43" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="M43" s="9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N43" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O43" s="12">
-        <v>0.40909090909090912</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="P43" s="11">
-        <v>41.128801702310852</v>
-      </c>
-      <c r="Q43" s="9"/>
+        <v>42.1</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E44" s="9">
-        <v>7393</v>
+        <v>10218</v>
       </c>
       <c r="F44" s="9">
-        <v>534</v>
+        <v>709</v>
       </c>
       <c r="G44" s="10">
-        <v>41.533707865168537</v>
+        <v>43.24</v>
       </c>
       <c r="H44" s="11">
-        <v>0.3125</v>
+        <v>0.3</v>
       </c>
       <c r="I44" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
@@ -3123,16 +3176,16 @@
         <v>60</v>
       </c>
       <c r="M44" s="9">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N44" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O44" s="12">
-        <v>0.375</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="P44" s="11">
-        <v>40.971759401109878</v>
+        <v>42</v>
       </c>
       <c r="Q44" s="9">
         <v>1</v>
@@ -3140,153 +3193,151 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E45" s="9">
-        <v>9450</v>
+        <v>13433</v>
       </c>
       <c r="F45" s="9">
-        <v>668</v>
+        <v>915</v>
       </c>
       <c r="G45" s="10">
-        <v>42.440119760479043</v>
+        <v>44.04</v>
       </c>
       <c r="H45" s="11">
         <v>0.5</v>
       </c>
       <c r="I45" s="9">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="M45" s="9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O45" s="12">
-        <v>0.35</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="P45" s="11">
-        <v>40.771075478025175</v>
+        <v>41.7</v>
       </c>
       <c r="Q45" s="9"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E46" s="9">
-        <v>11739</v>
+        <v>11396</v>
       </c>
       <c r="F46" s="9">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="G46" s="10">
-        <v>41.480565371024738</v>
+        <v>40.89</v>
       </c>
       <c r="H46" s="11">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="I46" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J46" s="9"/>
       <c r="K46" s="9"/>
       <c r="L46" s="9">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M46" s="9">
         <v>24</v>
       </c>
       <c r="N46" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O46" s="12">
-        <v>0.29166666666666669</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="P46" s="11">
-        <v>38.534814802583064</v>
-      </c>
-      <c r="Q46" s="9">
-        <v>1</v>
-      </c>
+        <v>41.6</v>
+      </c>
+      <c r="Q46" s="9"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E47" s="9">
-        <v>10546</v>
+        <v>11415</v>
       </c>
       <c r="F47" s="9">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="G47" s="10">
-        <v>39.746231155778894</v>
+        <v>42.33</v>
       </c>
       <c r="H47" s="11">
-        <v>0.27272727272727271</v>
+        <v>0.5</v>
       </c>
       <c r="I47" s="9">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
       <c r="L47" s="9">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M47" s="9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N47" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O47" s="12">
-        <v>0.31818181818181818</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="P47" s="11">
-        <v>38.17159554415916</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="Q47" s="9"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>24</v>
@@ -3295,71 +3346,71 @@
         <v>17</v>
       </c>
       <c r="E48" s="9">
-        <v>10385</v>
+        <v>12506</v>
       </c>
       <c r="F48" s="9">
-        <v>776</v>
+        <v>949</v>
       </c>
       <c r="G48" s="10">
-        <v>40.148195876288661</v>
+        <v>39.53</v>
       </c>
       <c r="H48" s="11">
-        <v>0.20833333333333334</v>
+        <v>0.3</v>
       </c>
       <c r="I48" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
       <c r="L48" s="9">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="M48" s="9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N48" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O48" s="12">
-        <v>0.33333333333333331</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="P48" s="11">
-        <v>37.59267800729971</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="Q48" s="9"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49" s="9">
-        <v>11715</v>
+        <v>12634</v>
       </c>
       <c r="F49" s="9">
-        <v>857</v>
+        <v>906</v>
       </c>
       <c r="G49" s="10">
-        <v>41.009334889148192</v>
+        <v>41.83</v>
       </c>
       <c r="H49" s="11">
-        <v>0.23076923076923078</v>
+        <v>0.4</v>
       </c>
       <c r="I49" s="9">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
       <c r="L49" s="9">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="M49" s="9">
         <v>26</v>
@@ -3368,10 +3419,10 @@
         <v>7</v>
       </c>
       <c r="O49" s="12">
-        <v>0.26923076923076922</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="P49" s="11">
-        <v>37.489056672494172</v>
+        <v>38.1</v>
       </c>
       <c r="Q49" s="9">
         <v>1</v>
@@ -3379,57 +3430,59 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E50" s="9">
-        <v>7998</v>
+        <v>13396</v>
       </c>
       <c r="F50" s="9">
-        <v>618</v>
+        <v>987</v>
       </c>
       <c r="G50" s="10">
-        <v>38.825242718446603</v>
+        <v>40.72</v>
       </c>
       <c r="H50" s="11">
-        <v>0.27777777777777779</v>
+        <v>0.2</v>
       </c>
       <c r="I50" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
       <c r="L50" s="9">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="M50" s="9">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="N50" s="9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O50" s="12">
-        <v>0.27777777777777779</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="P50" s="11">
-        <v>35.848604770342575</v>
-      </c>
-      <c r="Q50" s="9"/>
+        <v>37.1</v>
+      </c>
+      <c r="Q50" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>24</v>
@@ -3438,108 +3491,110 @@
         <v>17</v>
       </c>
       <c r="E51" s="9">
-        <v>9919</v>
+        <v>11827</v>
       </c>
       <c r="F51" s="9">
-        <v>789</v>
+        <v>884</v>
       </c>
       <c r="G51" s="10">
-        <v>37.714828897338407</v>
+        <v>40.14</v>
       </c>
       <c r="H51" s="11">
-        <v>0.16666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="I51" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
       <c r="L51" s="9">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="M51" s="9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O51" s="12">
-        <v>0.25</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="P51" s="11">
-        <v>33.266438503625999</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="Q51" s="9"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E52" s="9">
-        <v>10663</v>
+        <v>11779</v>
       </c>
       <c r="F52" s="9">
-        <v>842</v>
+        <v>905</v>
       </c>
       <c r="G52" s="10">
-        <v>37.9916864608076</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="H52" s="11">
-        <v>0</v>
-      </c>
-      <c r="I52" s="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="I52" s="9">
+        <v>7</v>
+      </c>
       <c r="J52" s="9"/>
       <c r="K52" s="9"/>
       <c r="L52" s="9">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="M52" s="9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O52" s="12">
-        <v>0.16666666666666666</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="P52" s="11">
-        <v>31.869608421192467</v>
+        <v>35.6</v>
       </c>
       <c r="Q52" s="9"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E53" s="9">
-        <v>10609</v>
+        <v>8648</v>
       </c>
       <c r="F53" s="9">
-        <v>848</v>
+        <v>663</v>
       </c>
       <c r="G53" s="10">
-        <v>37.531839622641513</v>
+        <v>39.130000000000003</v>
       </c>
       <c r="H53" s="11">
-        <v>0.20833333333333334</v>
+        <v>0.3</v>
       </c>
       <c r="I53" s="9">
         <v>5</v>
@@ -3547,124 +3602,120 @@
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
       <c r="L53" s="9">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M53" s="9">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N53" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53" s="12">
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="P53" s="11">
-        <v>31.442379179932534</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="Q53" s="9"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E54" s="9">
-        <v>5994</v>
+        <v>10663</v>
       </c>
       <c r="F54" s="9">
-        <v>462</v>
+        <v>842</v>
       </c>
       <c r="G54" s="10">
-        <v>38.922077922077918</v>
-      </c>
-      <c r="H54" s="11">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="I54" s="9">
-        <v>2</v>
-      </c>
+        <v>37.99</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="I54" s="9"/>
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
       <c r="L54" s="9">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M54" s="9">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N54" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O54" s="12">
-        <v>7.1428571428571425E-2</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="P54" s="11">
-        <v>29.496136363636364</v>
+        <v>31.9</v>
       </c>
       <c r="Q54" s="9"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E55" s="9">
-        <v>2004</v>
+        <v>10609</v>
       </c>
       <c r="F55" s="9">
-        <v>113</v>
+        <v>848</v>
       </c>
       <c r="G55" s="10">
-        <v>53.203539823008853</v>
+        <v>37.53</v>
       </c>
       <c r="H55" s="11">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I55" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
       <c r="L55" s="9">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="M55" s="9">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="N55" s="9">
         <v>4</v>
       </c>
       <c r="O55" s="12">
-        <v>1</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="P55" s="11">
-        <v>68.487373497786209</v>
-      </c>
-      <c r="Q55" s="9">
-        <v>1</v>
-      </c>
+        <v>31.4</v>
+      </c>
+      <c r="Q55" s="9"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>38</v>
@@ -3673,880 +3724,882 @@
         <v>14</v>
       </c>
       <c r="E56" s="9">
-        <v>1918</v>
+        <v>7565</v>
       </c>
       <c r="F56" s="9">
-        <v>107</v>
+        <v>591</v>
       </c>
       <c r="G56" s="10">
-        <v>53.775700934579433</v>
+        <v>38.4</v>
       </c>
       <c r="H56" s="11">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="I56" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
+      <c r="L56" s="9">
+        <v>35</v>
+      </c>
       <c r="M56" s="9">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N56" s="9">
         <v>2</v>
       </c>
       <c r="O56" s="12">
+        <v>0.111</v>
+      </c>
+      <c r="P56" s="11">
+        <v>30.4</v>
+      </c>
+      <c r="Q56" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="15">
+        <v>2004</v>
+      </c>
+      <c r="F57" s="15">
+        <v>113</v>
+      </c>
+      <c r="G57" s="15">
+        <v>53.2</v>
+      </c>
+      <c r="H57" s="15">
+        <v>1</v>
+      </c>
+      <c r="I57" s="15">
+        <v>4</v>
+      </c>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15">
+        <v>36</v>
+      </c>
+      <c r="M57" s="15">
+        <v>4</v>
+      </c>
+      <c r="N57" s="15">
+        <v>4</v>
+      </c>
+      <c r="O57" s="16">
+        <v>1</v>
+      </c>
+      <c r="P57" s="15">
+        <v>68.5</v>
+      </c>
+      <c r="Q57" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="15">
+        <v>1918</v>
+      </c>
+      <c r="F58" s="15">
+        <v>107</v>
+      </c>
+      <c r="G58" s="15">
+        <v>53.78</v>
+      </c>
+      <c r="H58" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="I58" s="15">
+        <v>3</v>
+      </c>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15">
+        <v>4</v>
+      </c>
+      <c r="N58" s="15">
+        <v>2</v>
+      </c>
+      <c r="O58" s="16">
         <v>0.5</v>
       </c>
-      <c r="P56" s="11">
-        <v>53.639733201581024</v>
-      </c>
-      <c r="Q56" s="9"/>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+      <c r="P58" s="15">
+        <v>53.6</v>
+      </c>
+      <c r="Q58" s="15"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B59" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C59" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D59" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E59" s="15">
         <v>1964</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F59" s="15">
         <v>145</v>
       </c>
-      <c r="G57" s="10">
-        <v>40.634482758620692</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="G59" s="15">
+        <v>40.630000000000003</v>
+      </c>
+      <c r="H59" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="I59" s="15">
+        <v>1</v>
+      </c>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="15">
+        <v>10</v>
+      </c>
+      <c r="M59" s="15">
+        <v>4</v>
+      </c>
+      <c r="N59" s="15">
+        <v>3</v>
+      </c>
+      <c r="O59" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="P59" s="15">
+        <v>51.2</v>
+      </c>
+      <c r="Q59" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="15">
+        <v>4439</v>
+      </c>
+      <c r="F60" s="15">
+        <v>311</v>
+      </c>
+      <c r="G60" s="15">
+        <v>42.82</v>
+      </c>
+      <c r="H60" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="I60" s="15">
+        <v>4</v>
+      </c>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15">
+        <v>34</v>
+      </c>
+      <c r="M60" s="15">
+        <v>9</v>
+      </c>
+      <c r="N60" s="15">
+        <v>6</v>
+      </c>
+      <c r="O60" s="16">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P60" s="15">
+        <v>50.8</v>
+      </c>
+      <c r="Q60" s="15"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="15">
+        <v>1971</v>
+      </c>
+      <c r="F61" s="15">
+        <v>127</v>
+      </c>
+      <c r="G61" s="15">
+        <v>46.56</v>
+      </c>
+      <c r="H61" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I61" s="15">
+        <v>2</v>
+      </c>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15">
+        <v>22</v>
+      </c>
+      <c r="M61" s="15">
+        <v>4</v>
+      </c>
+      <c r="N61" s="15">
+        <v>2</v>
+      </c>
+      <c r="O61" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="P61" s="15">
+        <v>47.9</v>
+      </c>
+      <c r="Q61" s="15"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="15">
+        <v>6056</v>
+      </c>
+      <c r="F62" s="15">
+        <v>406</v>
+      </c>
+      <c r="G62" s="15">
+        <v>44.75</v>
+      </c>
+      <c r="H62" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I62" s="15">
+        <v>2</v>
+      </c>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15">
+        <v>64</v>
+      </c>
+      <c r="M62" s="15">
+        <v>13</v>
+      </c>
+      <c r="N62" s="15">
+        <v>5</v>
+      </c>
+      <c r="O62" s="16">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="P62" s="15">
+        <v>43.7</v>
+      </c>
+      <c r="Q62" s="15"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="15">
+        <v>6011</v>
+      </c>
+      <c r="F63" s="15">
+        <v>422</v>
+      </c>
+      <c r="G63" s="15">
+        <v>42.73</v>
+      </c>
+      <c r="H63" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="I63" s="15">
+        <v>4</v>
+      </c>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15">
+        <v>72</v>
+      </c>
+      <c r="M63" s="15">
+        <v>13</v>
+      </c>
+      <c r="N63" s="15">
+        <v>5</v>
+      </c>
+      <c r="O63" s="16">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="P63" s="15">
+        <v>42.3</v>
+      </c>
+      <c r="Q63" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="15">
+        <v>1800</v>
+      </c>
+      <c r="F64" s="15">
+        <v>150</v>
+      </c>
+      <c r="G64" s="15">
+        <v>36</v>
+      </c>
+      <c r="H64" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1</v>
+      </c>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15">
+        <v>38</v>
+      </c>
+      <c r="M64" s="15">
+        <v>4</v>
+      </c>
+      <c r="N64" s="15">
+        <v>2</v>
+      </c>
+      <c r="O64" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="P64" s="15">
+        <v>40.1</v>
+      </c>
+      <c r="Q64" s="15"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="15">
+        <v>7150</v>
+      </c>
+      <c r="F65" s="15">
+        <v>535</v>
+      </c>
+      <c r="G65" s="15">
+        <v>40.090000000000003</v>
+      </c>
+      <c r="H65" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="I65" s="15">
+        <v>4</v>
+      </c>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15">
+        <v>20</v>
+      </c>
+      <c r="M65" s="15">
+        <v>15</v>
+      </c>
+      <c r="N65" s="15">
+        <v>5</v>
+      </c>
+      <c r="O65" s="16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="P65" s="15">
+        <v>38.6</v>
+      </c>
+      <c r="Q65" s="15"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="15">
+        <v>5502</v>
+      </c>
+      <c r="F66" s="15">
+        <v>409</v>
+      </c>
+      <c r="G66" s="15">
+        <v>40.36</v>
+      </c>
+      <c r="H66" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I66" s="15">
+        <v>6</v>
+      </c>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15">
+        <v>65</v>
+      </c>
+      <c r="M66" s="15">
+        <v>12</v>
+      </c>
+      <c r="N66" s="15">
+        <v>3</v>
+      </c>
+      <c r="O66" s="16">
         <v>0.25</v>
       </c>
-      <c r="I57" s="9">
+      <c r="P66" s="15">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="Q66" s="15">
         <v>1</v>
       </c>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9">
-        <v>10</v>
-      </c>
-      <c r="M57" s="9">
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="15">
+        <v>5388</v>
+      </c>
+      <c r="F67" s="15">
+        <v>408</v>
+      </c>
+      <c r="G67" s="15">
+        <v>39.619999999999997</v>
+      </c>
+      <c r="H67" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="I67" s="15">
+        <v>3</v>
+      </c>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15">
+        <v>16</v>
+      </c>
+      <c r="M67" s="15">
+        <v>12</v>
+      </c>
+      <c r="N67" s="15">
+        <v>3</v>
+      </c>
+      <c r="O67" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="P67" s="15">
+        <v>35.9</v>
+      </c>
+      <c r="Q67" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="15">
+        <v>1862</v>
+      </c>
+      <c r="F68" s="15">
+        <v>155</v>
+      </c>
+      <c r="G68" s="15">
+        <v>36.04</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15">
         <v>4</v>
       </c>
-      <c r="N57" s="9">
-        <v>3</v>
-      </c>
-      <c r="O57" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="P57" s="11">
-        <v>51.175829238329236</v>
-      </c>
-      <c r="Q57" s="9">
+      <c r="M68" s="15">
+        <v>4</v>
+      </c>
+      <c r="N68" s="15">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C58" s="9" t="s">
+      <c r="O68" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="P68" s="15">
+        <v>32.9</v>
+      </c>
+      <c r="Q68" s="15"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="15">
+        <v>3177</v>
+      </c>
+      <c r="F69" s="15">
+        <v>240</v>
+      </c>
+      <c r="G69" s="15">
+        <v>39.71</v>
+      </c>
+      <c r="H69" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="I69" s="15">
+        <v>2</v>
+      </c>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15">
+        <v>57</v>
+      </c>
+      <c r="M69" s="15">
+        <v>7</v>
+      </c>
+      <c r="N69" s="15">
+        <v>1</v>
+      </c>
+      <c r="O69" s="16">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="P69" s="15">
+        <v>32.5</v>
+      </c>
+      <c r="Q69" s="15"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="15">
+        <v>1804</v>
+      </c>
+      <c r="F70" s="15">
+        <v>159</v>
+      </c>
+      <c r="G70" s="15">
+        <v>34.04</v>
+      </c>
+      <c r="H70" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="I70" s="15">
+        <v>1</v>
+      </c>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15">
+        <v>16</v>
+      </c>
+      <c r="M70" s="15">
+        <v>4</v>
+      </c>
+      <c r="N70" s="15">
+        <v>1</v>
+      </c>
+      <c r="O70" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="P70" s="15">
+        <v>31.2</v>
+      </c>
+      <c r="Q70" s="15"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="15">
+        <v>3176</v>
+      </c>
+      <c r="F71" s="15">
+        <v>272</v>
+      </c>
+      <c r="G71" s="15">
+        <v>35.03</v>
+      </c>
+      <c r="H71" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I71" s="15">
+        <v>4</v>
+      </c>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15">
+        <v>2</v>
+      </c>
+      <c r="M71" s="15">
+        <v>8</v>
+      </c>
+      <c r="N71" s="15">
+        <v>1</v>
+      </c>
+      <c r="O71" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="P71" s="15">
+        <v>28.2</v>
+      </c>
+      <c r="Q71" s="15"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="15">
+        <v>1531</v>
+      </c>
+      <c r="F72" s="15">
+        <v>123</v>
+      </c>
+      <c r="G72" s="15">
+        <v>37.340000000000003</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="15"/>
+      <c r="M72" s="15">
+        <v>4</v>
+      </c>
+      <c r="N72" s="15">
+        <v>0</v>
+      </c>
+      <c r="O72" s="16">
+        <v>0</v>
+      </c>
+      <c r="P72" s="15">
+        <v>26.2</v>
+      </c>
+      <c r="Q72" s="15"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D73" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="9">
-        <v>4439</v>
-      </c>
-      <c r="F58" s="9">
-        <v>311</v>
-      </c>
-      <c r="G58" s="10">
-        <v>42.819935691318328</v>
-      </c>
-      <c r="H58" s="11">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="I58" s="9">
+      <c r="E73" s="15">
+        <v>2479</v>
+      </c>
+      <c r="F73" s="15">
+        <v>213</v>
+      </c>
+      <c r="G73" s="15">
+        <v>34.92</v>
+      </c>
+      <c r="H73" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I73" s="15">
+        <v>1</v>
+      </c>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="15">
+        <v>6</v>
+      </c>
+      <c r="N73" s="15">
+        <v>0</v>
+      </c>
+      <c r="O73" s="16">
+        <v>0</v>
+      </c>
+      <c r="P73" s="15">
+        <v>24.2</v>
+      </c>
+      <c r="Q73" s="15"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="15">
+        <v>1691</v>
+      </c>
+      <c r="F74" s="15">
+        <v>147</v>
+      </c>
+      <c r="G74" s="15">
+        <v>34.51</v>
+      </c>
+      <c r="H74" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="15"/>
+      <c r="M74" s="15">
         <v>4</v>
       </c>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9">
-        <v>34</v>
-      </c>
-      <c r="M58" s="9">
-        <v>9</v>
-      </c>
-      <c r="N58" s="9">
-        <v>6</v>
-      </c>
-      <c r="O58" s="12">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="P58" s="11">
-        <v>50.755926999509093</v>
-      </c>
-      <c r="Q58" s="9"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="9">
-        <v>5812</v>
-      </c>
-      <c r="F59" s="9">
-        <v>410</v>
-      </c>
-      <c r="G59" s="10">
-        <v>42.526829268292687</v>
-      </c>
-      <c r="H59" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I59" s="9">
-        <v>5</v>
-      </c>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9">
-        <v>64</v>
-      </c>
-      <c r="M59" s="9">
-        <v>12</v>
-      </c>
-      <c r="N59" s="9">
-        <v>7</v>
-      </c>
-      <c r="O59" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="P59" s="11">
-        <v>47.945664335664333</v>
-      </c>
-      <c r="Q59" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="9">
-        <v>5383</v>
-      </c>
-      <c r="F60" s="9">
-        <v>304</v>
-      </c>
-      <c r="G60" s="10">
-        <v>53.121710526315795</v>
-      </c>
-      <c r="H60" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="I60" s="9">
-        <v>9</v>
-      </c>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="9">
-        <v>86</v>
-      </c>
-      <c r="M60" s="9">
-        <v>12</v>
-      </c>
-      <c r="N60" s="9">
-        <v>4</v>
-      </c>
-      <c r="O60" s="12">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="P60" s="11">
-        <v>47.939410570761375</v>
-      </c>
-      <c r="Q60" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="9">
-        <v>1971</v>
-      </c>
-      <c r="F61" s="9">
-        <v>127</v>
-      </c>
-      <c r="G61" s="10">
-        <v>46.559055118110237</v>
-      </c>
-      <c r="H61" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I61" s="9">
-        <v>2</v>
-      </c>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9">
-        <v>22</v>
-      </c>
-      <c r="M61" s="9">
-        <v>4</v>
-      </c>
-      <c r="N61" s="9">
-        <v>2</v>
-      </c>
-      <c r="O61" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="P61" s="11">
-        <v>47.875037878787879</v>
-      </c>
-      <c r="Q61" s="9"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="9">
-        <v>6056</v>
-      </c>
-      <c r="F62" s="9">
-        <v>406</v>
-      </c>
-      <c r="G62" s="10">
-        <v>44.748768472906406</v>
-      </c>
-      <c r="H62" s="11">
-        <v>0.15384615384615385</v>
-      </c>
-      <c r="I62" s="9">
-        <v>2</v>
-      </c>
-      <c r="J62" s="9"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9">
-        <v>64</v>
-      </c>
-      <c r="M62" s="9">
-        <v>13</v>
-      </c>
-      <c r="N62" s="9">
-        <v>5</v>
-      </c>
-      <c r="O62" s="12">
-        <v>0.38461538461538464</v>
-      </c>
-      <c r="P62" s="11">
-        <v>43.723837123837114</v>
-      </c>
-      <c r="Q62" s="9"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E63" s="9">
-        <v>6011</v>
-      </c>
-      <c r="F63" s="9">
-        <v>422</v>
-      </c>
-      <c r="G63" s="10">
-        <v>42.732227488151658</v>
-      </c>
-      <c r="H63" s="11">
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="I63" s="9">
-        <v>4</v>
-      </c>
-      <c r="J63" s="9"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9">
-        <v>72</v>
-      </c>
-      <c r="M63" s="9">
-        <v>13</v>
-      </c>
-      <c r="N63" s="9">
-        <v>5</v>
-      </c>
-      <c r="O63" s="12">
-        <v>0.38461538461538464</v>
-      </c>
-      <c r="P63" s="11">
-        <v>42.29754266132349</v>
-      </c>
-      <c r="Q63" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E64" s="9">
-        <v>1800</v>
-      </c>
-      <c r="F64" s="9">
-        <v>150</v>
-      </c>
-      <c r="G64" s="10">
-        <v>36</v>
-      </c>
-      <c r="H64" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="I64" s="9">
-        <v>1</v>
-      </c>
-      <c r="J64" s="9"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="9">
-        <v>38</v>
-      </c>
-      <c r="M64" s="9">
-        <v>4</v>
-      </c>
-      <c r="N64" s="9">
-        <v>2</v>
-      </c>
-      <c r="O64" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="P64" s="11">
-        <v>40.056146680216798</v>
-      </c>
-      <c r="Q64" s="9"/>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E65" s="9">
-        <v>5730</v>
-      </c>
-      <c r="F65" s="9">
-        <v>441</v>
-      </c>
-      <c r="G65" s="10">
-        <v>38.979591836734691</v>
-      </c>
-      <c r="H65" s="11">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="I65" s="9">
-        <v>4</v>
-      </c>
-      <c r="J65" s="9"/>
-      <c r="K65" s="9"/>
-      <c r="L65" s="9">
-        <v>20</v>
-      </c>
-      <c r="M65" s="9">
-        <v>12</v>
-      </c>
-      <c r="N65" s="9">
-        <v>4</v>
-      </c>
-      <c r="O65" s="12">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="P65" s="11">
-        <v>37.634297743773551</v>
-      </c>
-      <c r="Q65" s="9"/>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="9">
-        <v>5502</v>
-      </c>
-      <c r="F66" s="9">
-        <v>409</v>
-      </c>
-      <c r="G66" s="10">
-        <v>40.356968215158922</v>
-      </c>
-      <c r="H66" s="11">
-        <v>5.75</v>
-      </c>
-      <c r="I66" s="9">
-        <v>69</v>
-      </c>
-      <c r="J66" s="9"/>
-      <c r="K66" s="9"/>
-      <c r="L66" s="9">
-        <v>65</v>
-      </c>
-      <c r="M66" s="9">
-        <v>12</v>
-      </c>
-      <c r="N66" s="9">
-        <v>3</v>
-      </c>
-      <c r="O66" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="P66" s="11">
-        <v>36.273025118089905</v>
-      </c>
-      <c r="Q66" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="9">
-        <v>5388</v>
-      </c>
-      <c r="F67" s="9">
-        <v>408</v>
-      </c>
-      <c r="G67" s="10">
-        <v>39.617647058823529</v>
-      </c>
-      <c r="H67" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="I67" s="9">
-        <v>3</v>
-      </c>
-      <c r="J67" s="9"/>
-      <c r="K67" s="9"/>
-      <c r="L67" s="9">
-        <v>16</v>
-      </c>
-      <c r="M67" s="9">
-        <v>12</v>
-      </c>
-      <c r="N67" s="9">
-        <v>3</v>
-      </c>
-      <c r="O67" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="P67" s="11">
-        <v>35.873746924371922</v>
-      </c>
-      <c r="Q67" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="9">
-        <v>1862</v>
-      </c>
-      <c r="F68" s="9">
-        <v>155</v>
-      </c>
-      <c r="G68" s="10">
-        <v>36.038709677419355</v>
-      </c>
-      <c r="H68" s="11">
+      <c r="N74" s="15">
         <v>0</v>
       </c>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
-      <c r="K68" s="9"/>
-      <c r="L68" s="9">
-        <v>4</v>
-      </c>
-      <c r="M68" s="9">
-        <v>4</v>
-      </c>
-      <c r="N68" s="9">
-        <v>1</v>
-      </c>
-      <c r="O68" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="P68" s="11">
-        <v>32.917743902439021</v>
-      </c>
-      <c r="Q68" s="9"/>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E69" s="9">
-        <v>3177</v>
-      </c>
-      <c r="F69" s="9">
-        <v>240</v>
-      </c>
-      <c r="G69" s="10">
-        <v>39.712500000000006</v>
-      </c>
-      <c r="H69" s="11">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="I69" s="9">
-        <v>2</v>
-      </c>
-      <c r="J69" s="9"/>
-      <c r="K69" s="9"/>
-      <c r="L69" s="9">
-        <v>57</v>
-      </c>
-      <c r="M69" s="9">
-        <v>7</v>
-      </c>
-      <c r="N69" s="9">
-        <v>1</v>
-      </c>
-      <c r="O69" s="12">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="P69" s="11">
-        <v>32.460951825951824</v>
-      </c>
-      <c r="Q69" s="9"/>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="9">
-        <v>1804</v>
-      </c>
-      <c r="F70" s="9">
-        <v>159</v>
-      </c>
-      <c r="G70" s="10">
-        <v>34.037735849056602</v>
-      </c>
-      <c r="H70" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="I70" s="9">
-        <v>1</v>
-      </c>
-      <c r="J70" s="9"/>
-      <c r="K70" s="9"/>
-      <c r="L70" s="9">
-        <v>16</v>
-      </c>
-      <c r="M70" s="9">
-        <v>4</v>
-      </c>
-      <c r="N70" s="9">
-        <v>1</v>
-      </c>
-      <c r="O70" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="P70" s="11">
-        <v>31.21590909090909</v>
-      </c>
-      <c r="Q70" s="9"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E71" s="9">
-        <v>1531</v>
-      </c>
-      <c r="F71" s="9">
-        <v>123</v>
-      </c>
-      <c r="G71" s="10">
-        <v>37.341463414634148</v>
-      </c>
-      <c r="H71" s="11">
+      <c r="O74" s="16">
         <v>0</v>
       </c>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9"/>
-      <c r="L71" s="9"/>
-      <c r="M71" s="9">
-        <v>4</v>
-      </c>
-      <c r="N71" s="9">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12">
-        <v>0</v>
-      </c>
-      <c r="P71" s="11">
-        <v>26.191666666666663</v>
-      </c>
-      <c r="Q71" s="9"/>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="9">
-        <v>2479</v>
-      </c>
-      <c r="F72" s="9">
-        <v>213</v>
-      </c>
-      <c r="G72" s="10">
-        <v>34.91549295774648</v>
-      </c>
-      <c r="H72" s="11">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="I72" s="9">
-        <v>1</v>
-      </c>
-      <c r="J72" s="9"/>
-      <c r="K72" s="9"/>
-      <c r="L72" s="9"/>
-      <c r="M72" s="9">
-        <v>6</v>
-      </c>
-      <c r="N72" s="9">
-        <v>0</v>
-      </c>
-      <c r="O72" s="12">
-        <v>0</v>
-      </c>
-      <c r="P72" s="11">
-        <v>24.222222222222218</v>
-      </c>
-      <c r="Q72" s="9"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E73" s="9">
-        <v>1691</v>
-      </c>
-      <c r="F73" s="9">
-        <v>147</v>
-      </c>
-      <c r="G73" s="10">
-        <v>34.510204081632651</v>
-      </c>
-      <c r="H73" s="11">
-        <v>0</v>
-      </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="9"/>
-      <c r="L73" s="9"/>
-      <c r="M73" s="9">
-        <v>4</v>
-      </c>
-      <c r="N73" s="9">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12">
-        <v>0</v>
-      </c>
-      <c r="P73" s="11">
-        <v>24.150096153846153</v>
-      </c>
-      <c r="Q73" s="9"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E74" s="9">
-        <v>1323</v>
-      </c>
-      <c r="F74" s="9">
-        <v>120</v>
-      </c>
-      <c r="G74" s="10">
-        <v>33.075000000000003</v>
-      </c>
-      <c r="H74" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="I74" s="9">
-        <v>1</v>
-      </c>
-      <c r="J74" s="9"/>
-      <c r="K74" s="9"/>
-      <c r="L74" s="9"/>
-      <c r="M74" s="9">
-        <v>4</v>
-      </c>
-      <c r="N74" s="9">
-        <v>0</v>
-      </c>
-      <c r="O74" s="12">
-        <v>0</v>
-      </c>
-      <c r="P74" s="11">
-        <v>23.26819444444444</v>
-      </c>
-      <c r="Q74" s="9"/>
+      <c r="P74" s="15">
+        <v>24.2</v>
+      </c>
+      <c r="Q74" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
